--- a/backend/data/financials_by_company/1BD.F.xlsx
+++ b/backend/data/financials_by_company/1BD.F.xlsx
@@ -3434,7 +3434,7 @@
         <v>1774915200</v>
       </c>
       <c r="BF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
         <v>1.6690648</v>
@@ -3596,7 +3596,7 @@
         <v>0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
